--- a/sheets/대금율보/검수/은행나무 침대.xlsx
+++ b/sheets/대금율보/검수/은행나무 침대.xlsx
@@ -1885,22 +1885,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="19.86" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="19.86" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="19.86" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="19.86" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="19.86" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="61.54" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.6" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.6" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -1965,7 +1965,7 @@
       <c r="J4" s="21"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.6" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="K5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.6" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="K6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.6" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.6" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="K8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.6" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.6" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -2125,7 +2125,7 @@
       <c r="J10" s="21"/>
       <c r="K10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.6" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="K11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.6" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="K12" s="26"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.6" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -2203,7 +2203,7 @@
       <c r="J13" s="21"/>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.6" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2241,6 +2241,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="65"/>
 </worksheet>
 </file>